--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484550_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484550_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0134</v>
+        <v>8.782299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.897</v>
+        <v>6.8393</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1163</v>
+        <v>1.9429</v>
       </c>
       <c r="G2" t="n">
         <v>6.4925</v>
@@ -610,13 +610,13 @@
         <v>3.1154</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9553</v>
+        <v>0.7242</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4276</v>
+        <v>0.3699</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.3542</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6335</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8098</v>
+        <v>7.0534</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5586</v>
+        <v>5.0426</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2512</v>
+        <v>2.0108</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9554</v>
+        <v>6.2833</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4741</v>
+        <v>3.6482</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4812</v>
+        <v>2.635</v>
       </c>
       <c r="J3" t="n">
-        <v>6.5601</v>
+        <v>6.8069</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1428</v>
+        <v>4.1398</v>
       </c>
       <c r="L3" t="n">
-        <v>3.4173</v>
+        <v>2.6672</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6047</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6686</v>
+        <v>-0.4916</v>
       </c>
       <c r="O3" t="n">
-        <v>0.064</v>
+        <v>-0.0321</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0158</v>
+        <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.206</v>
+        <v>0.0371</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0015</v>
+        <v>0.0683</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2045</v>
+        <v>-0.0311</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7842</v>
+        <v>6.7224</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6991</v>
+        <v>6.174</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0851</v>
+        <v>0.5485</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2833</v>
+        <v>5.9554</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6482</v>
+        <v>2.4741</v>
       </c>
       <c r="I4" t="n">
-        <v>2.635</v>
+        <v>3.4812</v>
       </c>
       <c r="J4" t="n">
-        <v>6.8069</v>
+        <v>6.5601</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1398</v>
+        <v>3.1428</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6672</v>
+        <v>3.4173</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.6047</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4916</v>
+        <v>-0.6686</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0321</v>
+        <v>0.064</v>
       </c>
       <c r="P4" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5656</v>
+        <v>2.0158</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2321</v>
+        <v>-0.2934</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2753</v>
+        <v>-0.3861</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0432</v>
+        <v>0.0927</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7926</v>
+        <v>4.3591</v>
       </c>
       <c r="E5" t="n">
-        <v>2.581</v>
+        <v>2.9245</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2117</v>
+        <v>1.4346</v>
       </c>
       <c r="G5" t="n">
         <v>1.6629</v>
@@ -844,13 +844,13 @@
         <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.42</v>
+        <v>0.1465</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4955</v>
+        <v>-0.152</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0755</v>
+        <v>0.2984</v>
       </c>
       <c r="V5" t="n">
         <v>1.267</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6993</v>
+        <v>3.3866</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1776</v>
+        <v>2.3951</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5217</v>
+        <v>0.9915</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9438</v>
+        <v>1.1705</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5209</v>
+        <v>1.2189</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.0483</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0066</v>
+        <v>2.2333</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4551</v>
+        <v>2.0249</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4486</v>
+        <v>0.2084</v>
       </c>
       <c r="M6" t="n">
         <v>-1.0627</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9342</v>
+        <v>-0.806</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1285</v>
+        <v>-0.2567</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>4.0317</v>
+        <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4781</v>
+        <v>-0.7002</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0746</v>
+        <v>-0.1889</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5528</v>
+        <v>-0.5113</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9109</v>
+        <v>1.267</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9109</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7898</v>
+        <v>3.2178</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9965</v>
+        <v>0.1916</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7933</v>
+        <v>3.0262</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1705</v>
+        <v>0.9438</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2189</v>
+        <v>1.5209</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0483</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2333</v>
+        <v>2.0066</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0249</v>
+        <v>2.4551</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2084</v>
+        <v>-0.4486</v>
       </c>
       <c r="M7" t="n">
         <v>-1.0627</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.806</v>
+        <v>-0.9342</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2567</v>
+        <v>-0.1285</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5656</v>
+        <v>4.0317</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.297</v>
+        <v>-0.0034</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5875</v>
+        <v>-0.0607</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7095</v>
+        <v>0.0573</v>
       </c>
       <c r="V7" t="n">
-        <v>1.267</v>
+        <v>1.9109</v>
       </c>
       <c r="W7" t="n">
-        <v>1.267</v>
+        <v>1.9109</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6742</v>
+        <v>1.6113</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7797</v>
+        <v>2.6425</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1055</v>
+        <v>-1.0312</v>
       </c>
       <c r="G8" t="n">
         <v>1.2951</v>
@@ -1078,13 +1078,13 @@
         <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1959</v>
+        <v>0.1329</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5309</v>
+        <v>0.3937</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3351</v>
+        <v>-0.2608</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4886</v>
+        <v>0.8351</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4965</v>
+        <v>1.7439</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0079</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>1.8177</v>
@@ -1312,13 +1312,13 @@
         <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5569</v>
+        <v>-0.2104</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6425</v>
+        <v>-0.3952</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0857</v>
+        <v>0.1847</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9554</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3481</v>
+        <v>0.4657</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4465</v>
+        <v>-0.8556</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0984</v>
+        <v>1.3213</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4703</v>
@@ -1390,13 +1390,13 @@
         <v>2.5656</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8777</v>
+        <v>-0.0639</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6425</v>
+        <v>-0.0516</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2352</v>
+        <v>-0.0123</v>
       </c>
       <c r="V12" t="n">
         <v>1.267</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1467</v>
+        <v>-0.9574</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1818</v>
+        <v>0.1066</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9649</v>
+        <v>-1.064</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3272</v>
@@ -1468,13 +1468,13 @@
         <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3406</v>
+        <v>-0.1512</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4404</v>
+        <v>-0.152</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0998</v>
+        <v>0.0007</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3115</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.3916</v>
+        <v>-1.3479</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6292</v>
+        <v>1.8215</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0208</v>
+        <v>-3.1694</v>
       </c>
       <c r="G14" t="n">
         <v>0.5551</v>
@@ -1546,13 +1546,13 @@
         <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1762</v>
+        <v>0.2198</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1471</v>
+        <v>0.0453</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3232</v>
+        <v>0.1746</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8559</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.9673</v>
+        <v>-4.3797</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.2798</v>
+        <v>-4.5683</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3125</v>
+        <v>0.1886</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2543</v>
@@ -1624,13 +1624,13 @@
         <v>2.7489</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3028</v>
+        <v>-0.1095</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1456</v>
+        <v>-0.1429</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1572</v>
+        <v>0.0334</v>
       </c>
       <c r="V15" t="n">
         <v>-1.267</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>32.37399999999999</v>
+        <v>32.92449999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>27.0829</v>
+        <v>27.6335</v>
       </c>
       <c r="F16" t="n">
-        <v>5.2911</v>
+        <v>5.291000000000003</v>
       </c>
       <c r="G16" t="n">
         <v>25.3003</v>
@@ -1678,7 +1678,7 @@
         <v>36.48350000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>22.6977</v>
+        <v>22.69769999999999</v>
       </c>
       <c r="L16" t="n">
         <v>13.7859</v>
@@ -1702,13 +1702,13 @@
         <v>26.5723</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8220000000000003</v>
+        <v>-0.2715</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2028</v>
+        <v>-0.6522</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3807999999999999</v>
+        <v>0.3805000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2668</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8997</v>
+        <v>1.3169</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7185</v>
+        <v>2.3339</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8187</v>
+        <v>-1.0169</v>
       </c>
       <c r="G17" t="n">
         <v>0.1315</v>
@@ -1780,13 +1780,13 @@
         <v>2.3823</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4621</v>
+        <v>0.8793</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0242</v>
+        <v>0.6395</v>
       </c>
       <c r="U17" t="n">
-        <v>0.438</v>
+        <v>0.2398</v>
       </c>
       <c r="V17" t="n">
         <v>1.5889</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTAÑES</t>
+          <t>J. REY SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6251</v>
+        <v>0.6596</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6251</v>
+        <v>-0.4977</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.1573</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6251</v>
+        <v>-0.6496</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1.1723</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6251</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6251</v>
+        <v>0.4525</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.4427</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6251</v>
+        <v>0.0098</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.1021</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.6149</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.5128</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.2517</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.1018</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.3535</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.5235</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MONFORTE MARTINEZ</t>
+          <t>L. SALVADOR MONTAÑES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4585</v>
+        <v>0.6251</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0243</v>
+        <v>0.6251</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5658</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.238</v>
+        <v>0.6251</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2057</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0323</v>
+        <v>0.6251</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4655</v>
+        <v>0.6251</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7987</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.6251</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7035</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0044</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6991</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.597</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2919</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3051</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. REY SANCHEZ</t>
+          <t>J. MONFORTE MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3434</v>
+        <v>0.1176</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6899999999999999</v>
+        <v>2.832</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0334</v>
+        <v>-2.7144</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6496</v>
+        <v>-1.238</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1723</v>
+        <v>-0.2057</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5227000000000001</v>
+        <v>-1.0323</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4525</v>
+        <v>1.4655</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4427</v>
+        <v>0.7987</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0098</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1021</v>
+        <v>-2.7035</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6149</v>
+        <v>-1.0044</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5128</v>
+        <v>-1.6991</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0645</v>
+        <v>0.256</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2941</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2296</v>
+        <v>0.1565</v>
       </c>
       <c r="V20" t="n">
-        <v>2.5235</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9005</v>
+        <v>1.267</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6231</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>O. FORNER LUCEA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1724</v>
+        <v>-1.4619</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1973</v>
+        <v>-2.0777</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.3697</v>
+        <v>0.6158</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2082</v>
+        <v>-1.4479</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1476</v>
+        <v>-0.6465</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9394</v>
+        <v>-0.8014</v>
       </c>
       <c r="J21" t="n">
-        <v>7.5874</v>
+        <v>-1.2387</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5453</v>
+        <v>-0.5977</v>
       </c>
       <c r="L21" t="n">
-        <v>2.042</v>
+        <v>-0.641</v>
       </c>
       <c r="M21" t="n">
-        <v>-6.3792</v>
+        <v>-0.2092</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.3977</v>
+        <v>-0.0489</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.9815</v>
+        <v>-0.1603</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3823</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1991</v>
+        <v>0.5498</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3029</v>
+        <v>0.3526</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4925</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1896</v>
+        <v>0.2753</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. FORNER LUCEA</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6862</v>
+        <v>-1.522</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1738</v>
+        <v>2.6204</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4876</v>
+        <v>-4.1424</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4479</v>
+        <v>1.2082</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6465</v>
+        <v>2.1476</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8014</v>
+        <v>-0.9394</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2387</v>
+        <v>7.5874</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5977</v>
+        <v>5.5453</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.641</v>
+        <v>2.042</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2092</v>
+        <v>-6.3792</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0489</v>
+        <v>-3.3977</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1603</v>
+        <v>-2.9815</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3665</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5498</v>
+        <v>2.1991</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1282</v>
+        <v>-0.0467</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0188</v>
+        <v>-0.0844</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1471</v>
+        <v>0.0377</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. VANOUKIA</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7072</v>
+        <v>-1.6645</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8733</v>
+        <v>0.4781</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8339</v>
+        <v>-2.1427</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4232</v>
+        <v>-1.9256</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8269</v>
+        <v>-0.4607</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5964</v>
+        <v>-1.465</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0603</v>
+        <v>0.506</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9254</v>
+        <v>1.1054</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1349</v>
+        <v>-0.5994</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.4836</v>
+        <v>-2.4317</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7523</v>
+        <v>-1.5661</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7312</v>
+        <v>-0.8656</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8156</v>
+        <v>-0.2886</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1818</v>
+        <v>-0.0279</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6338</v>
+        <v>-0.2608</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>M. VANOUKIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9312</v>
+        <v>-1.9913</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2858</v>
+        <v>-1.1617</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.217</v>
+        <v>-0.8296</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9256</v>
+        <v>-2.4232</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4607</v>
+        <v>-0.8269</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.465</v>
+        <v>-1.5964</v>
       </c>
       <c r="J24" t="n">
-        <v>0.506</v>
+        <v>1.0603</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1054</v>
+        <v>0.9254</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5994</v>
+        <v>0.1349</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4317</v>
+        <v>-3.4836</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5661</v>
+        <v>-1.7523</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8656</v>
+        <v>-1.7312</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5498</v>
+        <v>-0.733</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5498</v>
+        <v>2.0158</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5553</v>
+        <v>0.5315</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2202</v>
+        <v>-0.1067</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3351</v>
+        <v>0.6382</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7851</v>
+        <v>-2.6598</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.504</v>
+        <v>-0.4078</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2811</v>
+        <v>-2.252</v>
       </c>
       <c r="G25" t="n">
         <v>-3.5728</v>
@@ -2404,13 +2404,13 @@
         <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1573</v>
+        <v>-0.0321</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3854</v>
+        <v>-0.2892</v>
       </c>
       <c r="U25" t="n">
-        <v>0.228</v>
+        <v>0.2572</v>
       </c>
       <c r="V25" t="n">
         <v>0.945</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9757</v>
+        <v>-3.2918</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6158</v>
+        <v>-0.8081</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3598</v>
+        <v>-2.4837</v>
       </c>
       <c r="G26" t="n">
         <v>-3.3878</v>
@@ -2482,13 +2482,13 @@
         <v>1.2828</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0456</v>
+        <v>-0.2705</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0355</v>
+        <v>-0.1568</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0102</v>
+        <v>-0.1137</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.9904</v>
+        <v>-5.6524</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.5035</v>
+        <v>-2.215</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.4869</v>
+        <v>-3.4374</v>
       </c>
       <c r="G27" t="n">
         <v>-3.0498</v>
@@ -2560,13 +2560,13 @@
         <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0401</v>
+        <v>0.2979</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2391</v>
+        <v>0.0494</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1989</v>
+        <v>0.2485</v>
       </c>
       <c r="V27" t="n">
         <v>-2.5339</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-7.9474</v>
+        <v>-6.945</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.7571</v>
+        <v>-2.1801</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.1903</v>
+        <v>-4.7648</v>
       </c>
       <c r="G28" t="n">
         <v>-4.04</v>
@@ -2638,13 +2638,13 @@
         <v>1.8326</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.1585</v>
+        <v>-0.1561</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.8446</v>
+        <v>-0.2677</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3139</v>
+        <v>0.1116</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-9.5054</v>
+        <v>-9.263500000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.0247</v>
+        <v>-4.8324</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.4807</v>
+        <v>-4.4311</v>
       </c>
       <c r="G29" t="n">
         <v>-5.5302</v>
@@ -2716,13 +2716,13 @@
         <v>1.8326</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.5537</v>
+        <v>-0.3118</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.4042</v>
+        <v>-0.2119</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1495</v>
+        <v>-0.0999</v>
       </c>
       <c r="V29" t="n">
         <v>-1.5889</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-32.37430000000001</v>
+        <v>-31.733</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.291199999999998</v>
+        <v>-5.291</v>
       </c>
       <c r="F30" t="n">
-        <v>-27.0829</v>
+        <v>-26.4419</v>
       </c>
       <c r="G30" t="n">
         <v>-25.3001</v>
@@ -2773,7 +2773,7 @@
         <v>10.3802</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8030999999999997</v>
+        <v>0.8031000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-36.4837</v>
@@ -2794,13 +2794,13 @@
         <v>17.4095</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8219999999999997</v>
+        <v>1.4632</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.3804999999999998</v>
+        <v>-0.3806</v>
       </c>
       <c r="U30" t="n">
-        <v>1.2026</v>
+        <v>1.8439</v>
       </c>
       <c r="V30" t="n">
         <v>1.267</v>
